--- a/Дело3а-78-2026Таганай/01_Иск/01.9_Прочее_процессуальное/ПОЯСНИТЕЛЬНАЯ ЗАПИСКА 2/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.9_Прочее_процессуальное/ПОЯСНИТЕЛЬНАЯ ЗАПИСКА 2/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92553506437</v>
+        <v>46157.93107470869</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.9_Прочее_процессуальное/ПОЯСНИТЕЛЬНАЯ ЗАПИСКА 2/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.9_Прочее_процессуальное/ПОЯСНИТЕЛЬНАЯ ЗАПИСКА 2/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93107470869</v>
+        <v>46157.93132409216</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.9_Прочее_процессуальное/ПОЯСНИТЕЛЬНАЯ ЗАПИСКА 2/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.9_Прочее_процессуальное/ПОЯСНИТЕЛЬНАЯ ЗАПИСКА 2/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93132409216</v>
+        <v>46157.93380357006</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.9_Прочее_процессуальное/ПОЯСНИТЕЛЬНАЯ ЗАПИСКА 2/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.9_Прочее_процессуальное/ПОЯСНИТЕЛЬНАЯ ЗАПИСКА 2/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93380357006</v>
+        <v>46157.9369103344</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.9_Прочее_процессуальное/ПОЯСНИТЕЛЬНАЯ ЗАПИСКА 2/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.9_Прочее_процессуальное/ПОЯСНИТЕЛЬНАЯ ЗАПИСКА 2/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.9369103344</v>
+        <v>46158.28203277702</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.9_Прочее_процессуальное/ПОЯСНИТЕЛЬНАЯ ЗАПИСКА 2/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.9_Прочее_процессуальное/ПОЯСНИТЕЛЬНАЯ ЗАПИСКА 2/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28203277702</v>
+        <v>46158.29734599009</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.9_Прочее_процессуальное/ПОЯСНИТЕЛЬНАЯ ЗАПИСКА 2/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.9_Прочее_процессуальное/ПОЯСНИТЕЛЬНАЯ ЗАПИСКА 2/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29734599009</v>
+        <v>46158.29803626706</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.9_Прочее_процессуальное/ПОЯСНИТЕЛЬНАЯ ЗАПИСКА 2/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.9_Прочее_процессуальное/ПОЯСНИТЕЛЬНАЯ ЗАПИСКА 2/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29803626706</v>
+        <v>46158.3336719417</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.9_Прочее_процессуальное/ПОЯСНИТЕЛЬНАЯ ЗАПИСКА 2/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.9_Прочее_процессуальное/ПОЯСНИТЕЛЬНАЯ ЗАПИСКА 2/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.3336719417</v>
+        <v>46158.37219044837</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.9_Прочее_процессуальное/ПОЯСНИТЕЛЬНАЯ ЗАПИСКА 2/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.9_Прочее_процессуальное/ПОЯСНИТЕЛЬНАЯ ЗАПИСКА 2/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.37219044837</v>
+        <v>46158.37273839502</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
